--- a/employee.xlsx
+++ b/employee.xlsx
@@ -443,7 +443,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>99000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="3">
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>85000</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Geeta</t>
+          <t>Shyam</t>
         </is>
       </c>
       <c r="C4" t="n">

--- a/employee.xlsx
+++ b/employee.xlsx
@@ -443,7 +443,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>90000</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="3">
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>45000</v>
+        <v>85000</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Shyam</t>
+          <t>Geeta</t>
         </is>
       </c>
       <c r="C4" t="n">
